--- a/results_experiments/canal_physical/comparison_all_images.xlsx
+++ b/results_experiments/canal_physical/comparison_all_images.xlsx
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>128.476517</v>
+        <v>14.912426</v>
       </c>
       <c r="E3" t="n">
         <v>25</v>
@@ -2643,12 +2643,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>above</t>
+          <t>below</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>a 3D length; a 2D section holds only part of a thread</t>
+          <t>owned length per cell divided by roots per cell; a 2D section holds only part of a thread, and ownership has no distance limit</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>276.782103</v>
+        <v>25.162009</v>
       </c>
       <c r="E7" t="n">
         <v>25</v>
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>above</t>
+          <t>inside</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>a 3D length; a 2D section holds only part of a thread</t>
+          <t>owned length per cell divided by roots per cell; a 2D section holds only part of a thread, and ownership has no distance limit</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>126.439989</v>
+        <v>15.284005</v>
       </c>
       <c r="E11" t="n">
         <v>25</v>
@@ -2971,12 +2971,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>above</t>
+          <t>below</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>a 3D length; a 2D section holds only part of a thread</t>
+          <t>owned length per cell divided by roots per cell; a 2D section holds only part of a thread, and ownership has no distance limit</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>310.179688</v>
+        <v>36.29743</v>
       </c>
       <c r="E15" t="n">
         <v>25</v>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>above</t>
+          <t>inside</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>a 3D length; a 2D section holds only part of a thread</t>
+          <t>owned length per cell divided by roots per cell; a 2D section holds only part of a thread, and ownership has no distance limit</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>219.353264</v>
+        <v>28.925832</v>
       </c>
       <c r="E19" t="n">
         <v>25</v>
@@ -3299,12 +3299,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>above</t>
+          <t>inside</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>a 3D length; a 2D section holds only part of a thread</t>
+          <t>owned length per cell divided by roots per cell; a 2D section holds only part of a thread, and ownership has no distance limit</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>454.531038</v>
+        <v>65.715014</v>
       </c>
       <c r="E23" t="n">
         <v>25</v>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>a 3D length; a 2D section holds only part of a thread</t>
+          <t>owned length per cell divided by roots per cell; a 2D section holds only part of a thread, and ownership has no distance limit</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>186.569097</v>
+        <v>27.082567</v>
       </c>
       <c r="E27" t="n">
         <v>25</v>
@@ -3627,12 +3627,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>above</t>
+          <t>inside</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>a 3D length; a 2D section holds only part of a thread</t>
+          <t>owned length per cell divided by roots per cell; a 2D section holds only part of a thread, and ownership has no distance limit</t>
         </is>
       </c>
     </row>
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>590.5319940000001</v>
+        <v>83.043691</v>
       </c>
       <c r="E31" t="n">
         <v>25</v>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>a 3D length; a 2D section holds only part of a thread</t>
+          <t>owned length per cell divided by roots per cell; a 2D section holds only part of a thread, and ownership has no distance limit</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>222.818258</v>
+        <v>33.121499</v>
       </c>
       <c r="E35" t="n">
         <v>25</v>
@@ -3955,12 +3955,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>above</t>
+          <t>inside</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>a 3D length; a 2D section holds only part of a thread</t>
+          <t>owned length per cell divided by roots per cell; a 2D section holds only part of a thread, and ownership has no distance limit</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>397.98655</v>
+        <v>62.541101</v>
       </c>
       <c r="E39" t="n">
         <v>25</v>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>a 3D length; a 2D section holds only part of a thread</t>
+          <t>owned length per cell divided by roots per cell; a 2D section holds only part of a thread, and ownership has no distance limit</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>241.872943</v>
+        <v>24.187294</v>
       </c>
       <c r="E43" t="n">
         <v>25</v>
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>above</t>
+          <t>below</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>a 3D length; a 2D section holds only part of a thread</t>
+          <t>owned length per cell divided by roots per cell; a 2D section holds only part of a thread, and ownership has no distance limit</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>443.696565</v>
+        <v>41.759677</v>
       </c>
       <c r="E47" t="n">
         <v>25</v>
@@ -4447,12 +4447,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>above</t>
+          <t>inside</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>a 3D length; a 2D section holds only part of a thread</t>
+          <t>owned length per cell divided by roots per cell; a 2D section holds only part of a thread, and ownership has no distance limit</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>138.556184</v>
+        <v>20.596106</v>
       </c>
       <c r="E51" t="n">
         <v>25</v>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>above</t>
+          <t>below</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>a 3D length; a 2D section holds only part of a thread</t>
+          <t>owned length per cell divided by roots per cell; a 2D section holds only part of a thread, and ownership has no distance limit</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>310.433409</v>
+        <v>45.530112</v>
       </c>
       <c r="E55" t="n">
         <v>25</v>
@@ -4775,12 +4775,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>above</t>
+          <t>inside</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>a 3D length; a 2D section holds only part of a thread</t>
+          <t>owned length per cell divided by roots per cell; a 2D section holds only part of a thread, and ownership has no distance limit</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>110.306898</v>
+        <v>19.891245</v>
       </c>
       <c r="E59" t="n">
         <v>25</v>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>above</t>
+          <t>below</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>a 3D length; a 2D section holds only part of a thread</t>
+          <t>owned length per cell divided by roots per cell; a 2D section holds only part of a thread, and ownership has no distance limit</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>337.023791</v>
+        <v>62.83537</v>
       </c>
       <c r="E63" t="n">
         <v>25</v>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>a 3D length; a 2D section holds only part of a thread</t>
+          <t>owned length per cell divided by roots per cell; a 2D section holds only part of a thread, and ownership has no distance limit</t>
         </is>
       </c>
     </row>
